--- a/StudentsPerformance.xlsx
+++ b/StudentsPerformance.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rajashahi\Desktop\shaheen 2025\Learn\archive (1)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rajashahi\Desktop\shaheen 2025\Learn\Project 1- StudentPreformance Analysis and Forecast\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F61ED407-56AE-48AC-9603-59A1AE0D510F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2CF3AD2-EC51-4C22-97B9-B40EED2FCBD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{BB50E81B-B635-4398-A58E-C71B62ED72FC}"/>
   </bookViews>
@@ -705,15 +705,15 @@
     <xf numFmtId="0" fontId="16" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="1" fontId="16" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="16" fillId="36" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="1" fontId="16" fillId="36" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="16" fillId="35" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="16" fillId="35" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="36" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="1" fontId="16" fillId="36" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -36264,11 +36264,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="5"/>
+      <c r="B1" s="8"/>
+      <c r="C1" s="4"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
@@ -36459,20 +36459,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="C2" s="6" t="s">
         <v>49</v>
       </c>
     </row>
@@ -36481,12 +36481,12 @@
         <v>100</v>
       </c>
       <c r="B3" s="3">
-        <f>FORECAST(A3,StudentsPerformance!F2:F1001,StudentsPerformance!G2:G1001)</f>
-        <v>92.267608332018227</v>
+        <f>FORECAST(A3,StudentsPerformance!G2:G1001,StudentsPerformance!F2:F1001)</f>
+        <v>95.864730743249936</v>
       </c>
       <c r="C3" s="3">
-        <f>_xlfn.FORECAST.LINEAR(A3,StudentsPerformance!F2:F1001,StudentsPerformance!G2:G1001)</f>
-        <v>92.267608332018227</v>
+        <f>_xlfn.FORECAST.LINEAR(A3,StudentsPerformance!G2:G1001,StudentsPerformance!F2:F1001)</f>
+        <v>95.864730743249936</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -36494,12 +36494,12 @@
         <v>90</v>
       </c>
       <c r="B4" s="3">
-        <f>FORECAST(A4,StudentsPerformance!F2:F1001,StudentsPerformance!G2:G1001)</f>
-        <v>83.776606310670161</v>
+        <f>FORECAST(A4,StudentsPerformance!G3:G1002,StudentsPerformance!F3:F1002)</f>
+        <v>87.973591590612941</v>
       </c>
       <c r="C4" s="3">
-        <f>_xlfn.FORECAST.LINEAR(A4,StudentsPerformance!F2:F1001,StudentsPerformance!G2:G1001)</f>
-        <v>83.776606310670161</v>
+        <f>_xlfn.FORECAST.LINEAR(A4,StudentsPerformance!G3:G1002,StudentsPerformance!F3:F1002)</f>
+        <v>87.973591590612941</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
@@ -36507,12 +36507,12 @@
         <v>80</v>
       </c>
       <c r="B5" s="3">
-        <f>FORECAST(A5,StudentsPerformance!F2:F1001,StudentsPerformance!G2:G1001)</f>
-        <v>75.285604289322094</v>
+        <f>FORECAST(A5,StudentsPerformance!G4:G1003,StudentsPerformance!F4:F1003)</f>
+        <v>80.11930973504758</v>
       </c>
       <c r="C5" s="3">
-        <f>_xlfn.FORECAST.LINEAR(A5,StudentsPerformance!F2:F1001,StudentsPerformance!G2:G1001)</f>
-        <v>75.285604289322094</v>
+        <f>_xlfn.FORECAST.LINEAR(A5,StudentsPerformance!G4:G1003,StudentsPerformance!F4:F1003)</f>
+        <v>80.11930973504758</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
@@ -36520,12 +36520,12 @@
         <v>70</v>
       </c>
       <c r="B6" s="3">
-        <f>FORECAST(A6,StudentsPerformance!F2:F1001,StudentsPerformance!G2:G1001)</f>
-        <v>66.794602267974028</v>
+        <f>FORECAST(A6,StudentsPerformance!G5:G1004,StudentsPerformance!F5:F1004)</f>
+        <v>72.24077623732309</v>
       </c>
       <c r="C6" s="3">
-        <f>_xlfn.FORECAST.LINEAR(A6,StudentsPerformance!F2:F1001,StudentsPerformance!G2:G1001)</f>
-        <v>66.794602267974028</v>
+        <f>_xlfn.FORECAST.LINEAR(A6,StudentsPerformance!G5:G1004,StudentsPerformance!F5:F1004)</f>
+        <v>72.24077623732309</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
@@ -36533,12 +36533,12 @@
         <v>60</v>
       </c>
       <c r="B7" s="3">
-        <f>FORECAST(A7,StudentsPerformance!F2:F1001,StudentsPerformance!G2:G1001)</f>
-        <v>58.303600246625962</v>
+        <f>FORECAST(A7,StudentsPerformance!G6:G1005,StudentsPerformance!F6:F1005)</f>
+        <v>64.375091090821883</v>
       </c>
       <c r="C7" s="3">
-        <f>_xlfn.FORECAST.LINEAR(A7,StudentsPerformance!F2:F1001,StudentsPerformance!G2:G1001)</f>
-        <v>58.303600246625962</v>
+        <f>_xlfn.FORECAST.LINEAR(A7,StudentsPerformance!G6:G1005,StudentsPerformance!F6:F1005)</f>
+        <v>64.375091090821883</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
@@ -36546,12 +36546,12 @@
         <v>50</v>
       </c>
       <c r="B8" s="3">
-        <f>FORECAST(A8,StudentsPerformance!F2:F1001,StudentsPerformance!G2:G1001)</f>
-        <v>49.812598225277902</v>
+        <f>FORECAST(A8,StudentsPerformance!G7:G1006,StudentsPerformance!F7:F1006)</f>
+        <v>56.511317506777011</v>
       </c>
       <c r="C8" s="3">
-        <f>_xlfn.FORECAST.LINEAR(A8,StudentsPerformance!F2:F1001,StudentsPerformance!G2:G1001)</f>
-        <v>49.812598225277902</v>
+        <f>_xlfn.FORECAST.LINEAR(A8,StudentsPerformance!G7:G1006,StudentsPerformance!F7:F1006)</f>
+        <v>56.511317506777011</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
@@ -36559,12 +36559,12 @@
         <v>40</v>
       </c>
       <c r="B9" s="3">
-        <f>FORECAST(A9,StudentsPerformance!F2:F1001,StudentsPerformance!G2:G1001)</f>
-        <v>41.321596203929836</v>
+        <f>FORECAST(A9,StudentsPerformance!G8:G1007,StudentsPerformance!F8:F1007)</f>
+        <v>48.660002701127929</v>
       </c>
       <c r="C9" s="3">
-        <f>_xlfn.FORECAST.LINEAR(A9,StudentsPerformance!F2:F1001,StudentsPerformance!G2:G1001)</f>
-        <v>41.321596203929836</v>
+        <f>_xlfn.FORECAST.LINEAR(A9,StudentsPerformance!G8:G1007,StudentsPerformance!F8:F1007)</f>
+        <v>48.660002701127929</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
@@ -36572,12 +36572,12 @@
         <v>30</v>
       </c>
       <c r="B10" s="3">
-        <f>FORECAST(A10,StudentsPerformance!F2:F1001,StudentsPerformance!G2:G1001)</f>
-        <v>32.830594182581777</v>
+        <f>FORECAST(A10,StudentsPerformance!G9:G1008,StudentsPerformance!F9:F1008)</f>
+        <v>40.821697417921371</v>
       </c>
       <c r="C10" s="3">
-        <f>_xlfn.FORECAST.LINEAR(A10,StudentsPerformance!F2:F1001,StudentsPerformance!G2:G1001)</f>
-        <v>32.830594182581777</v>
+        <f>_xlfn.FORECAST.LINEAR(A10,StudentsPerformance!G9:G1008,StudentsPerformance!F9:F1008)</f>
+        <v>40.821697417921371</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
@@ -36585,12 +36585,12 @@
         <v>20</v>
       </c>
       <c r="B11" s="3">
-        <f>FORECAST(A11,StudentsPerformance!F2:F1001,StudentsPerformance!G2:G1001)</f>
-        <v>24.33959216123371</v>
+        <f>FORECAST(A11,StudentsPerformance!G10:G1009,StudentsPerformance!F10:F1009)</f>
+        <v>33.000383195317156</v>
       </c>
       <c r="C11" s="3">
-        <f>_xlfn.FORECAST.LINEAR(A11,StudentsPerformance!F2:F1001,StudentsPerformance!G2:G1001)</f>
-        <v>24.33959216123371</v>
+        <f>_xlfn.FORECAST.LINEAR(A11,StudentsPerformance!G10:G1009,StudentsPerformance!F10:F1009)</f>
+        <v>33.000383195317156</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
@@ -36598,12 +36598,12 @@
         <v>10</v>
       </c>
       <c r="B12" s="3">
-        <f>FORECAST(A12,StudentsPerformance!F2:F1001,StudentsPerformance!G2:G1001)</f>
-        <v>15.848590139885648</v>
+        <f>FORECAST(A12,StudentsPerformance!G11:G1010,StudentsPerformance!F11:F1010)</f>
+        <v>25.142529698775821</v>
       </c>
       <c r="C12" s="3">
-        <f>_xlfn.FORECAST.LINEAR(A12,StudentsPerformance!F2:F1001,StudentsPerformance!G2:G1001)</f>
-        <v>15.848590139885648</v>
+        <f>_xlfn.FORECAST.LINEAR(A12,StudentsPerformance!G11:G1010,StudentsPerformance!F11:F1010)</f>
+        <v>25.142529698775821</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
@@ -36611,12 +36611,12 @@
         <v>0</v>
       </c>
       <c r="B13" s="3">
-        <f>FORECAST(A13,StudentsPerformance!F2:F1001,StudentsPerformance!G2:G1001)</f>
-        <v>7.3575881185375849</v>
+        <f>FORECAST(A13,StudentsPerformance!G12:G1011,StudentsPerformance!F12:F1011)</f>
+        <v>17.224486836498805</v>
       </c>
       <c r="C13" s="3">
-        <f>_xlfn.FORECAST.LINEAR(A13,StudentsPerformance!F2:F1001,StudentsPerformance!G2:G1001)</f>
-        <v>7.3575881185375849</v>
+        <f>_xlfn.FORECAST.LINEAR(A13,StudentsPerformance!G12:G1011,StudentsPerformance!F12:F1011)</f>
+        <v>17.224486836498805</v>
       </c>
     </row>
   </sheetData>
